--- a/Calibration/Calibrations.xlsx
+++ b/Calibration/Calibrations.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="16">
   <si>
     <t>LABR_1</t>
   </si>
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A5:G65"/>
+  <dimension ref="A5:G107"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11.625" bestFit="1" customWidth="1"/>
@@ -1115,6 +1115,398 @@
       <c r="G65">
         <f t="shared" si="0"/>
         <v>5.2991774721886288E-6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>0</v>
+      </c>
+      <c r="B72">
+        <v>1</v>
+      </c>
+      <c r="C72">
+        <v>6689.93</v>
+      </c>
+      <c r="D72">
+        <v>96280.3</v>
+      </c>
+      <c r="E72">
+        <v>1549.96</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>1</v>
+      </c>
+      <c r="B73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>2</v>
+      </c>
+      <c r="B74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>3</v>
+      </c>
+      <c r="B75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>4</v>
+      </c>
+      <c r="B76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>5</v>
+      </c>
+      <c r="B77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>6</v>
+      </c>
+      <c r="B78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>7</v>
+      </c>
+      <c r="B79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>8</v>
+      </c>
+      <c r="B80">
+        <v>1</v>
+      </c>
+      <c r="C80">
+        <v>7422.63</v>
+      </c>
+      <c r="D80">
+        <v>92348.2</v>
+      </c>
+      <c r="E80">
+        <v>1506.11</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>9</v>
+      </c>
+      <c r="B81">
+        <v>1</v>
+      </c>
+      <c r="C81">
+        <v>8315.0499999999993</v>
+      </c>
+      <c r="D81">
+        <v>86805.1</v>
+      </c>
+      <c r="E81">
+        <v>1324.07</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>10</v>
+      </c>
+      <c r="B82">
+        <v>1</v>
+      </c>
+      <c r="C82">
+        <v>8210.35</v>
+      </c>
+      <c r="D82">
+        <v>83806</v>
+      </c>
+      <c r="E82">
+        <v>1325.53</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>11</v>
+      </c>
+      <c r="B83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>12</v>
+      </c>
+      <c r="B84">
+        <v>1</v>
+      </c>
+      <c r="C84">
+        <v>7908.49</v>
+      </c>
+      <c r="D84">
+        <v>87527.9</v>
+      </c>
+      <c r="E84">
+        <v>1399.81</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>13</v>
+      </c>
+      <c r="B85">
+        <v>1</v>
+      </c>
+      <c r="C85">
+        <v>8125.65</v>
+      </c>
+      <c r="D85">
+        <v>88831</v>
+      </c>
+      <c r="E85">
+        <v>1343.32</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>14</v>
+      </c>
+      <c r="B86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87">
+        <v>1</v>
+      </c>
+      <c r="C87">
+        <v>7175.11</v>
+      </c>
+      <c r="D87">
+        <v>85356.7</v>
+      </c>
+      <c r="E87">
+        <v>1391.22</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>0</v>
+      </c>
+      <c r="B92">
+        <v>1</v>
+      </c>
+      <c r="C92">
+        <v>8502.49</v>
+      </c>
+      <c r="D92">
+        <v>148759</v>
+      </c>
+      <c r="E92">
+        <v>2272.6799999999998</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>1</v>
+      </c>
+      <c r="B93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>2</v>
+      </c>
+      <c r="B94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>3</v>
+      </c>
+      <c r="B95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>4</v>
+      </c>
+      <c r="B96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>5</v>
+      </c>
+      <c r="B97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>6</v>
+      </c>
+      <c r="B98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>7</v>
+      </c>
+      <c r="B99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>8</v>
+      </c>
+      <c r="B100">
+        <v>1</v>
+      </c>
+      <c r="C100">
+        <v>6285.85</v>
+      </c>
+      <c r="D100">
+        <v>155273</v>
+      </c>
+      <c r="E100">
+        <v>2402.75</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>9</v>
+      </c>
+      <c r="B101">
+        <v>1</v>
+      </c>
+      <c r="C101">
+        <v>6251.32</v>
+      </c>
+      <c r="D101">
+        <v>155740</v>
+      </c>
+      <c r="E101">
+        <v>2245.64</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>10</v>
+      </c>
+      <c r="B102">
+        <v>1</v>
+      </c>
+      <c r="C102">
+        <v>5527.29</v>
+      </c>
+      <c r="D102">
+        <v>166383</v>
+      </c>
+      <c r="E102">
+        <v>2383.4699999999998</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>11</v>
+      </c>
+      <c r="B103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>12</v>
+      </c>
+      <c r="B104">
+        <v>1</v>
+      </c>
+      <c r="C104">
+        <v>5778.37</v>
+      </c>
+      <c r="D104">
+        <v>156706</v>
+      </c>
+      <c r="E104">
+        <v>2355.4299999999998</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>13</v>
+      </c>
+      <c r="B105">
+        <v>1</v>
+      </c>
+      <c r="C105">
+        <v>6344.02</v>
+      </c>
+      <c r="D105">
+        <v>150081</v>
+      </c>
+      <c r="E105">
+        <v>2119.88</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>14</v>
+      </c>
+      <c r="B106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107">
+        <v>1</v>
+      </c>
+      <c r="C107">
+        <v>4777.97</v>
+      </c>
+      <c r="D107">
+        <v>170242</v>
+      </c>
+      <c r="E107">
+        <v>2630.63</v>
       </c>
     </row>
   </sheetData>

--- a/Calibration/Calibrations.xlsx
+++ b/Calibration/Calibrations.xlsx
@@ -1138,6 +1138,10 @@
       <c r="E72">
         <v>1549.96</v>
       </c>
+      <c r="G72">
+        <f t="shared" ref="G72" si="1">0.66165/D72</f>
+        <v>6.8721223344754842E-6</v>
+      </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
@@ -1211,8 +1215,12 @@
       <c r="E80">
         <v>1506.11</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G80">
+        <f>0.66165/D80</f>
+        <v>7.1647308772666928E-6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>9</v>
       </c>
@@ -1228,8 +1236,12 @@
       <c r="E81">
         <v>1324.07</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G81">
+        <f>0.66165/D81</f>
+        <v>7.6222480015575116E-6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>10</v>
       </c>
@@ -1245,8 +1257,12 @@
       <c r="E82">
         <v>1325.53</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G82">
+        <f t="shared" ref="G80:G87" si="2">0.66165/D82</f>
+        <v>7.8950194496814062E-6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>11</v>
       </c>
@@ -1254,7 +1270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>12</v>
       </c>
@@ -1270,8 +1286,12 @@
       <c r="E84">
         <v>1399.81</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G84">
+        <f t="shared" si="2"/>
+        <v>7.5593039476555474E-6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>13</v>
       </c>
@@ -1287,8 +1307,12 @@
       <c r="E85">
         <v>1343.32</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G85">
+        <f>0.66165/D85</f>
+        <v>7.4484132791480445E-6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>14</v>
       </c>
@@ -1296,7 +1320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>15</v>
       </c>
@@ -1312,13 +1336,17 @@
       <c r="E87">
         <v>1391.22</v>
       </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G87">
+        <f t="shared" si="2"/>
+        <v>7.7515883346005649E-6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>943</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>0</v>
       </c>
@@ -1334,8 +1362,12 @@
       <c r="E92">
         <v>2272.6799999999998</v>
       </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G92">
+        <f t="shared" ref="G92" si="3">0.66165/D92</f>
+        <v>4.4477981164164856E-6</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>1</v>
       </c>
@@ -1343,7 +1375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>2</v>
       </c>
@@ -1351,7 +1383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>3</v>
       </c>
@@ -1359,7 +1391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>4</v>
       </c>
@@ -1367,7 +1399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>5</v>
       </c>
@@ -1375,7 +1407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>6</v>
       </c>
@@ -1383,7 +1415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>7</v>
       </c>
@@ -1391,7 +1423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>8</v>
       </c>
@@ -1407,8 +1439,12 @@
       <c r="E100">
         <v>2402.75</v>
       </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G100">
+        <f t="shared" ref="G100:G107" si="4">0.66165/D100</f>
+        <v>4.261204459242753E-6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>9</v>
       </c>
@@ -1424,8 +1460,12 @@
       <c r="E101">
         <v>2245.64</v>
       </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G101">
+        <f t="shared" si="4"/>
+        <v>4.2484268652883006E-6</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>10</v>
       </c>
@@ -1441,8 +1481,12 @@
       <c r="E102">
         <v>2383.4699999999998</v>
       </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G102">
+        <f t="shared" si="4"/>
+        <v>3.9766682894286072E-6</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>11</v>
       </c>
@@ -1450,7 +1494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>12</v>
       </c>
@@ -1466,8 +1510,12 @@
       <c r="E104">
         <v>2355.4299999999998</v>
       </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G104">
+        <f t="shared" si="4"/>
+        <v>4.2222378211427766E-6</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>13</v>
       </c>
@@ -1483,8 +1531,12 @@
       <c r="E105">
         <v>2119.88</v>
       </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G105">
+        <f t="shared" si="4"/>
+        <v>4.4086193455534011E-6</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>14</v>
       </c>
@@ -1492,7 +1544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>15</v>
       </c>
@@ -1507,6 +1559,10 @@
       </c>
       <c r="E107">
         <v>2630.63</v>
+      </c>
+      <c r="G107">
+        <f t="shared" si="4"/>
+        <v>3.8865262391184313E-6</v>
       </c>
     </row>
   </sheetData>

--- a/Calibration/Calibrations.xlsx
+++ b/Calibration/Calibrations.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="30" windowWidth="27240" windowHeight="12780"/>
+    <workbookView xWindow="240" yWindow="30" windowWidth="27240" windowHeight="12780" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="21">
   <si>
     <t>LABR_1</t>
   </si>
@@ -64,12 +64,30 @@
   </si>
   <si>
     <t>LABR_16</t>
+  </si>
+  <si>
+    <t>Bi first peak</t>
+  </si>
+  <si>
+    <t>Parameter fit</t>
+  </si>
+  <si>
+    <t>Corrected Parametr</t>
+  </si>
+  <si>
+    <t>Exp</t>
+  </si>
+  <si>
+    <t>Corrected vo2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="0.000E+00"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -99,8 +117,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -464,7 +487,7 @@
         <v>1808.62</v>
       </c>
       <c r="G13">
-        <f t="shared" ref="G12:G65" si="0">0.66165/D13</f>
+        <f t="shared" ref="G13:G65" si="0">0.66165/D13</f>
         <v>5.4109863508860881E-6</v>
       </c>
     </row>
@@ -1258,7 +1281,7 @@
         <v>1325.53</v>
       </c>
       <c r="G82">
-        <f t="shared" ref="G80:G87" si="2">0.66165/D82</f>
+        <f t="shared" ref="G82:G87" si="2">0.66165/D82</f>
         <v>7.8950194496814062E-6</v>
       </c>
     </row>
@@ -1573,9 +1596,286 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A6:G22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7">
+        <v>0.56969800000000004</v>
+      </c>
+      <c r="C7" s="1">
+        <v>5.4E-6</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1" t="e">
+        <f>C7*B7/D7</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>0.56969800000000004</v>
+      </c>
+      <c r="C8" s="1">
+        <v>5.4E-6</v>
+      </c>
+      <c r="E8" s="3" t="e">
+        <f t="shared" ref="E8:E22" si="0">C8*B8/D8</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F8">
+        <v>0.56698999999999999</v>
+      </c>
+      <c r="G8" s="2" t="e">
+        <f>E8*B8/F8</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9">
+        <v>0.56969800000000004</v>
+      </c>
+      <c r="C9" s="1">
+        <v>5.4E-6</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10">
+        <v>0.56969800000000004</v>
+      </c>
+      <c r="C10" s="1">
+        <v>5.4E-6</v>
+      </c>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11">
+        <v>0.56969800000000004</v>
+      </c>
+      <c r="C11" s="1">
+        <v>5.4E-6</v>
+      </c>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12">
+        <v>0.56969800000000004</v>
+      </c>
+      <c r="C12" s="1">
+        <v>5.4E-6</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13">
+        <v>0.56969800000000004</v>
+      </c>
+      <c r="C13" s="1">
+        <v>5.4E-6</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14">
+        <v>0.56969800000000004</v>
+      </c>
+      <c r="C14" s="1">
+        <v>5.4E-6</v>
+      </c>
+      <c r="E14" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15">
+        <v>0.56969800000000004</v>
+      </c>
+      <c r="C15" s="1">
+        <v>5.4E-6</v>
+      </c>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16">
+        <v>0.56969800000000004</v>
+      </c>
+      <c r="C16" s="1">
+        <v>5.4E-6</v>
+      </c>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17">
+        <v>0.56969800000000004</v>
+      </c>
+      <c r="C17" s="1">
+        <v>5.4E-6</v>
+      </c>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18">
+        <v>0.56969800000000004</v>
+      </c>
+      <c r="C18" s="1">
+        <v>5.4E-6</v>
+      </c>
+      <c r="E18" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19">
+        <v>0.56969800000000004</v>
+      </c>
+      <c r="C19" s="1">
+        <v>5.4E-6</v>
+      </c>
+      <c r="E19" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20">
+        <v>0.56969800000000004</v>
+      </c>
+      <c r="C20" s="1">
+        <v>5.4E-6</v>
+      </c>
+      <c r="E20" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21">
+        <v>0.56969800000000004</v>
+      </c>
+      <c r="C21" s="1">
+        <v>5.4E-6</v>
+      </c>
+      <c r="E21" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22">
+        <v>0.56969800000000004</v>
+      </c>
+      <c r="C22" s="1">
+        <v>5.4E-6</v>
+      </c>
+      <c r="E22" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Calibration/Calibrations.xlsx
+++ b/Calibration/Calibrations.xlsx
@@ -121,9 +121,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1629,10 +1627,12 @@
       <c r="C7" s="1">
         <v>5.4E-6</v>
       </c>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1" t="e">
+      <c r="D7" s="1">
+        <v>0.28242200000000001</v>
+      </c>
+      <c r="E7" s="3">
         <f>C7*B7/D7</f>
-        <v>#DIV/0!</v>
+        <v>1.0892810050208555E-5</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1645,16 +1645,19 @@
       <c r="C8" s="1">
         <v>5.4E-6</v>
       </c>
-      <c r="E8" s="3" t="e">
+      <c r="D8">
+        <v>0.30315199999999998</v>
+      </c>
+      <c r="E8" s="3">
         <f t="shared" ref="E8:E22" si="0">C8*B8/D8</f>
-        <v>#DIV/0!</v>
+        <v>1.0147942946112844E-5</v>
       </c>
       <c r="F8">
         <v>0.56698999999999999</v>
       </c>
-      <c r="G8" s="2" t="e">
+      <c r="G8" s="2">
         <f>E8*B8/F8</f>
-        <v>#DIV/0!</v>
+        <v>1.0196410519611625E-5</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1667,10 +1670,12 @@
       <c r="C9" s="1">
         <v>5.4E-6</v>
       </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="D9" s="1">
+        <v>0.28655999999999998</v>
+      </c>
+      <c r="E9" s="3">
+        <f t="shared" si="0"/>
+        <v>1.0735515075376886E-5</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1683,10 +1688,12 @@
       <c r="C10" s="1">
         <v>5.4E-6</v>
       </c>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="D10" s="1">
+        <v>0.27921000000000001</v>
+      </c>
+      <c r="E10" s="3">
+        <f t="shared" si="0"/>
+        <v>1.1018119694853337E-5</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1699,10 +1706,12 @@
       <c r="C11" s="1">
         <v>5.4E-6</v>
       </c>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="D11" s="1">
+        <v>0.28045900000000001</v>
+      </c>
+      <c r="E11" s="3">
+        <f t="shared" si="0"/>
+        <v>1.0969051447805205E-5</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1715,10 +1724,12 @@
       <c r="C12" s="1">
         <v>5.4E-6</v>
       </c>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="D12" s="1">
+        <v>0.27410000000000001</v>
+      </c>
+      <c r="E12" s="3">
+        <f t="shared" si="0"/>
+        <v>1.1223528639182782E-5</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1731,10 +1742,12 @@
       <c r="C13" s="1">
         <v>5.4E-6</v>
       </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="D13" s="1">
+        <v>0.28191100000000002</v>
+      </c>
+      <c r="E13" s="3">
+        <f t="shared" si="0"/>
+        <v>1.0912554671509803E-5</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1747,9 +1760,12 @@
       <c r="C14" s="1">
         <v>5.4E-6</v>
       </c>
-      <c r="E14" s="1" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="D14">
+        <v>0.27620400000000001</v>
+      </c>
+      <c r="E14" s="3">
+        <f t="shared" si="0"/>
+        <v>1.1138032758395969E-5</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1762,10 +1778,12 @@
       <c r="C15" s="1">
         <v>5.4E-6</v>
       </c>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="D15" s="1">
+        <v>0.28827399999999997</v>
+      </c>
+      <c r="E15" s="3">
+        <f t="shared" si="0"/>
+        <v>1.0671684577866893E-5</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1778,10 +1796,12 @@
       <c r="C16" s="1">
         <v>5.4E-6</v>
       </c>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="D16" s="1">
+        <v>0.27010899999999999</v>
+      </c>
+      <c r="E16" s="3">
+        <f t="shared" si="0"/>
+        <v>1.1389362072348573E-5</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -1794,10 +1814,12 @@
       <c r="C17" s="1">
         <v>5.4E-6</v>
       </c>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="D17" s="1">
+        <v>0.28104699999999999</v>
+      </c>
+      <c r="E17" s="3">
+        <f t="shared" si="0"/>
+        <v>1.0946102253359761E-5</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -1810,9 +1832,12 @@
       <c r="C18" s="1">
         <v>5.4E-6</v>
       </c>
-      <c r="E18" s="1" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="D18">
+        <v>0.28648299999999999</v>
+      </c>
+      <c r="E18" s="3">
+        <f t="shared" si="0"/>
+        <v>1.0738400533364984E-5</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -1825,9 +1850,12 @@
       <c r="C19" s="1">
         <v>5.4E-6</v>
       </c>
-      <c r="E19" s="1" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="D19">
+        <v>0.276534</v>
+      </c>
+      <c r="E19" s="3">
+        <f t="shared" si="0"/>
+        <v>1.112474126147237E-5</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -1840,9 +1868,12 @@
       <c r="C20" s="1">
         <v>5.4E-6</v>
       </c>
-      <c r="E20" s="1" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="D20">
+        <v>0.27142500000000003</v>
+      </c>
+      <c r="E20" s="3">
+        <f t="shared" si="0"/>
+        <v>1.1334140922906881E-5</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -1855,9 +1886,12 @@
       <c r="C21" s="1">
         <v>5.4E-6</v>
       </c>
-      <c r="E21" s="1" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="D21">
+        <v>0.30953199999999997</v>
+      </c>
+      <c r="E21" s="3">
+        <f t="shared" si="0"/>
+        <v>9.9387759585438678E-6</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -1870,13 +1904,17 @@
       <c r="C22" s="1">
         <v>5.4E-6</v>
       </c>
-      <c r="E22" s="1" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="D22">
+        <v>0.27019100000000001</v>
+      </c>
+      <c r="E22" s="3">
+        <f t="shared" si="0"/>
+        <v>1.1385905526090804E-5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
